--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Global Advantage Fund (FOF).xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Global Advantage Fund (FOF).xlsx
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Global Advantage Fund (FOF)</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -97,7 +97,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -109,7 +109,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - S&amp;P Global 1200 Index (80%) +  BSE Sensex TRI (20%)</t>
+    <t>Benchmark name - S&amp;P Global 1200 Index (80%) + S&amp;P BSE Sensex TRI (20%)</t>
   </si>
 </sst>
 </file>
@@ -903,10 +903,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="9">
-        <v>32388.71</v>
+        <v>31551.02</v>
       </c>
       <c r="G5" s="10">
-        <v>0.9899367653073</v>
+        <v>0.9869460490717</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>12</v>
@@ -929,10 +929,10 @@
         <v>15400390.081</v>
       </c>
       <c r="F6" s="15">
-        <v>11071.34</v>
+        <v>10355.22</v>
       </c>
       <c r="G6" s="16">
-        <v>0.3383872499775</v>
+        <v>0.3239211748548</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>12</v>
@@ -952,13 +952,13 @@
         <v>15</v>
       </c>
       <c r="E7" s="14">
-        <v>2613300</v>
+        <v>2178477</v>
       </c>
       <c r="F7" s="15">
-        <v>9157</v>
+        <v>8433.32</v>
       </c>
       <c r="G7" s="16">
-        <v>0.2798768756125</v>
+        <v>0.2638023066943</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>12</v>
@@ -981,10 +981,10 @@
         <v>29161796.806</v>
       </c>
       <c r="F8" s="15">
-        <v>6243.69</v>
+        <v>6623.31</v>
       </c>
       <c r="G8" s="16">
-        <v>0.1908337282399</v>
+        <v>0.2071834646321</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>12</v>
@@ -1007,10 +1007,10 @@
         <v>19183834.112</v>
       </c>
       <c r="F9" s="15">
-        <v>5916.68</v>
+        <v>6139.17</v>
       </c>
       <c r="G9" s="16">
-        <v>0.1808389114774</v>
+        <v>0.1920391028905</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>12</v>
@@ -1041,10 +1041,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="9">
-        <v>31.67</v>
+        <v>763.85</v>
       </c>
       <c r="G11" s="10">
-        <v>0.0009679699301</v>
+        <v>0.0238939577732</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>12</v>
@@ -1075,10 +1075,10 @@
         <v>12</v>
       </c>
       <c r="F13" s="18">
-        <v>297.5784949900044</v>
+        <v>-346.53694910000195</v>
       </c>
       <c r="G13" s="19">
-        <v>0.009095264762181652</v>
+        <v>-0.010840006845156598</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>12</v>
@@ -1101,10 +1101,10 @@
         <v>12</v>
       </c>
       <c r="F14" s="18">
-        <v>32717.95849499</v>
+        <v>31968.3330509</v>
       </c>
       <c r="G14" s="19">
-        <v>0.9999999999995818</v>
+        <v>0.9999999999997433</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>12</v>
